--- a/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0001T0006Z000C1N13_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0001T0006Z000C1N13_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>8.178795058842111</v>
+        <v>1.329054197061843</v>
       </c>
       <c r="D2" t="n">
-        <v>9.524745793490723</v>
+        <v>1.547771191442243</v>
       </c>
       <c r="E2" t="n">
-        <v>16.06580348552658</v>
+        <v>2.61069306639807</v>
       </c>
       <c r="F2" t="n">
-        <v>15.47798153555199</v>
+        <v>2.515171999527198</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>15.97211004885209</v>
+        <v>2.595467882938464</v>
       </c>
       <c r="D3" t="n">
-        <v>16.09462667005339</v>
+        <v>2.615376833883676</v>
       </c>
       <c r="E3" t="n">
-        <v>16.06580348552658</v>
+        <v>2.61069306639807</v>
       </c>
       <c r="F3" t="n">
-        <v>15.47798153555199</v>
+        <v>2.515171999527198</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>24.52145917541174</v>
+        <v>3.984737116004407</v>
       </c>
       <c r="D4" t="n">
-        <v>20.13999192289019</v>
+        <v>3.272748687469656</v>
       </c>
       <c r="E4" t="n">
-        <v>16.06580348552658</v>
+        <v>2.61069306639807</v>
       </c>
       <c r="F4" t="n">
-        <v>15.47798153555199</v>
+        <v>2.515171999527198</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>56.91484763747462</v>
+        <v>9.248662741089626</v>
       </c>
       <c r="D5" t="n">
-        <v>40.64509631235404</v>
+        <v>6.604828150757532</v>
       </c>
       <c r="E5" t="n">
-        <v>16.06580348552658</v>
+        <v>2.61069306639807</v>
       </c>
       <c r="F5" t="n">
-        <v>15.47798153555199</v>
+        <v>2.515171999527198</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>13.80010174216445</v>
+        <v>2.242516533101723</v>
       </c>
       <c r="D6" t="n">
-        <v>31.75110954482398</v>
+        <v>5.159555301033897</v>
       </c>
       <c r="E6" t="n">
-        <v>16.06580348552658</v>
+        <v>2.61069306639807</v>
       </c>
       <c r="F6" t="n">
-        <v>15.47798153555199</v>
+        <v>2.515171999527198</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>16.42515479003297</v>
+        <v>2.669087653380358</v>
       </c>
       <c r="D7" t="n">
-        <v>54.88532376402824</v>
+        <v>8.918865111654588</v>
       </c>
       <c r="E7" t="n">
-        <v>16.06580348552658</v>
+        <v>2.61069306639807</v>
       </c>
       <c r="F7" t="n">
-        <v>15.47798153555199</v>
+        <v>2.515171999527198</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
